--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-catalogue.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-catalogue.xlsx
@@ -991,7 +991,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 10:30:30</t>
+          <t>2026-10-14 14:14:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-catalogue.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-catalogue.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -828,6 +828,23 @@
       <c r="C25" t="inlineStr">
         <is>
           <t>http://schema.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PREFIX</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>hrishapes</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>http://data.health-ri.nl/core/p2/</t>
         </is>
       </c>
     </row>
@@ -853,7 +870,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#aux-CatalogShape</t>
+          <t>http://data.health-ri.nl/core/p2/aux-CatalogShape</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -991,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 14:14:48</t>
+          <t>2026-10-14 14:30:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -1215,7 +1232,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hri:CatalogShape</t>
+          <t>hrishapes:CatalogShape</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1265,7 +1282,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#CatalogShape</t>
+          <t>http://data.health-ri.nl/core/p2/CatalogShape</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -1684,12 +1701,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>hri:CatalogShape/dcatap:applicableLegislation</t>
+          <t>hrishapes:CatalogShape#dcatap:applicableLegislation</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hri:CatalogShape</t>
+          <t>hrishapes:CatalogShape</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1742,12 +1759,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>hri:CatalogShape/dcat:catalog</t>
+          <t>hrishapes:CatalogShape#dcat:catalog</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>hri:CatalogShape</t>
+          <t>hrishapes:CatalogShape</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1800,12 +1817,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hri:CatalogShape/dcat:contactPoint</t>
+          <t>hrishapes:CatalogShape#dcat:contactPoint</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>hri:CatalogShape</t>
+          <t>hrishapes:CatalogShape</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1862,12 +1879,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>hri:CatalogShape/dct:creator</t>
+          <t>hrishapes:CatalogShape#dct:creator</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hri:CatalogShape</t>
+          <t>hrishapes:CatalogShape</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1920,12 +1937,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>hri:CatalogShape/dcat:dataset</t>
+          <t>hrishapes:CatalogShape#dcat:dataset</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hri:CatalogShape</t>
+          <t>hrishapes:CatalogShape</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1978,12 +1995,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hri:CatalogShape/dct:description</t>
+          <t>hrishapes:CatalogShape#dct:description</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hri:CatalogShape</t>
+          <t>hrishapes:CatalogShape</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2040,12 +2057,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>hri:CatalogShape/dct:spatial</t>
+          <t>hrishapes:CatalogShape#dct:spatial</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>hri:CatalogShape</t>
+          <t>hrishapes:CatalogShape</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2098,12 +2115,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>hri:CatalogShape/dct:hasPart</t>
+          <t>hrishapes:CatalogShape#dct:hasPart</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>hri:CatalogShape</t>
+          <t>hrishapes:CatalogShape</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2156,12 +2173,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>hri:CatalogShape/foaf:homepage</t>
+          <t>hrishapes:CatalogShape#foaf:homepage</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hri:CatalogShape</t>
+          <t>hrishapes:CatalogShape</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2216,12 +2233,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>hri:CatalogShape/dct:language</t>
+          <t>hrishapes:CatalogShape#dct:language</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hri:CatalogShape</t>
+          <t>hrishapes:CatalogShape</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2274,12 +2291,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>hri:CatalogShape/dct:license</t>
+          <t>hrishapes:CatalogShape#dct:license</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hri:CatalogShape</t>
+          <t>hrishapes:CatalogShape</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2334,12 +2351,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>hri:CatalogShape/dct:modified</t>
+          <t>hrishapes:CatalogShape#dct:modified</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>hri:CatalogShape</t>
+          <t>hrishapes:CatalogShape</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2402,12 +2419,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>hri:CatalogShape/dct:publisher</t>
+          <t>hrishapes:CatalogShape#dct:publisher</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>hri:CatalogShape</t>
+          <t>hrishapes:CatalogShape</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2464,12 +2481,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>hri:CatalogShape/dct:issued</t>
+          <t>hrishapes:CatalogShape#dct:issued</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>hri:CatalogShape</t>
+          <t>hrishapes:CatalogShape</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2532,12 +2549,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>hri:CatalogShape/dct:rights</t>
+          <t>hrishapes:CatalogShape#dct:rights</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>hri:CatalogShape</t>
+          <t>hrishapes:CatalogShape</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2592,12 +2609,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>hri:CatalogShape/dcat:service</t>
+          <t>hrishapes:CatalogShape#dcat:service</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>hri:CatalogShape</t>
+          <t>hrishapes:CatalogShape</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2646,12 +2663,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>hri:CatalogShape/dct:temporal</t>
+          <t>hrishapes:CatalogShape#dct:temporal</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>hri:CatalogShape</t>
+          <t>hrishapes:CatalogShape</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2704,12 +2721,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>hri:CatalogShape/dcat:themeTaxonomy</t>
+          <t>hrishapes:CatalogShape#dcat:themeTaxonomy</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>hri:CatalogShape</t>
+          <t>hrishapes:CatalogShape</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2762,12 +2779,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>hri:CatalogShape/dct:title</t>
+          <t>hrishapes:CatalogShape#dct:title</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>hri:CatalogShape</t>
+          <t>hrishapes:CatalogShape</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-catalogue.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-catalogue.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 14:30:37</t>
+          <t>2026-10-19 15:50:02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#KindShape</t>
+          <t>http://data.health-ri.nl/core/p2/KindShape</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1909,7 +1909,7 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#AgentShape</t>
+          <t>http://data.health-ri.nl/core/p2/AgentShape</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -2339,7 +2339,7 @@
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -2453,7 +2453,7 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#AgentShape</t>
+          <t>http://data.health-ri.nl/core/p2/AgentShape</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -2635,7 +2635,11 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>sh:IRI</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -2693,7 +2697,7 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#PeriodOfTimeShape</t>
+          <t>http://data.health-ri.nl/core/p2/PeriodOfTimeShape</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-catalogue.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-catalogue.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-19 15:50:02</t>
+          <t>2026-10-26 13:15:49</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-catalogue.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-catalogue.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-26 13:15:49</t>
+          <t>2026-10-26 16:19:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-catalogue.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-catalogue.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-26 16:19:38</t>
+          <t>2026-10-27 15:44:12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-catalogue.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-catalogue.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 15:44:12</t>
+          <t>2026-10-28 09:50:41</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-catalogue.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-catalogue.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-28 09:50:41</t>
+          <t>2026-10-28 11:04:12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
